--- a/data/trans_orig/P79_n_R3-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P79_n_R3-Habitat-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7014</t>
+          <t>6808</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>700</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3559</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2664</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>700</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7391</t>
+          <t>7575</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19054</t>
+          <t>24129</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11970</t>
+          <t>14769</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30982</t>
+          <t>36258</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18930</t>
+          <t>21632</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>14963</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28124</t>
+          <t>32323</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>37985</t>
+          <t>45761</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27477</t>
+          <t>33833</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51624</t>
+          <t>61409</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>29833</t>
+          <t>35364</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21176</t>
+          <t>25955</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>39875</t>
+          <t>49363</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>51784</t>
+          <t>60062</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>39264</t>
+          <t>48190</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65234</t>
+          <t>73857</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>81617</t>
+          <t>95426</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>66563</t>
+          <t>79935</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>98143</t>
+          <t>114884</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>584556</t>
+          <t>629225</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>570619</t>
+          <t>612068</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>597733</t>
+          <t>644018</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>653950</t>
+          <t>651786</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>638179</t>
+          <t>635944</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>669544</t>
+          <t>667431</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1238506</t>
+          <t>1281011</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1215151</t>
+          <t>1259443</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1257576</t>
+          <t>1301551</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>91,34%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6287</t>
+          <t>6618</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19895</t>
+          <t>16028</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7387</t>
+          <t>8851</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14185</t>
+          <t>15638</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>13673</t>
+          <t>15469</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7077</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>27196</t>
+          <t>27653</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>29742</t>
+          <t>34638</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14548</t>
+          <t>24519</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44818</t>
+          <t>50403</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>34422</t>
+          <t>39948</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25409</t>
+          <t>28915</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46958</t>
+          <t>53913</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>64164</t>
+          <t>74586</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40898</t>
+          <t>58702</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82789</t>
+          <t>92398</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>81463</t>
+          <t>93187</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40422</t>
+          <t>74274</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>115224</t>
+          <t>116008</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>84668</t>
+          <t>97047</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71275</t>
+          <t>81595</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>100946</t>
+          <t>116380</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>166131</t>
+          <t>190235</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>109109</t>
+          <t>164600</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>199886</t>
+          <t>218793</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1075372</t>
+          <t>914473</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1033429</t>
+          <t>888932</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1139254</t>
+          <t>937759</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>832174</t>
+          <t>925628</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>814598</t>
+          <t>903069</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>849234</t>
+          <t>943737</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1907547</t>
+          <t>1840101</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1862652</t>
+          <t>1806094</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1990789</t>
+          <t>1869761</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>88,18%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,67 +1863,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5592</t>
+          <t>5583</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14412</t>
+          <t>14453</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>6455</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2532</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>18129</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
           <t>0,79%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,05%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>7897</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1766</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>27161</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>13489</t>
+          <t>12038</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4494</t>
+          <t>5646</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>31398</t>
+          <t>23959</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -1976,67 +1976,67 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22523</t>
+          <t>24186</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14117</t>
+          <t>15347</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38865</t>
+          <t>39710</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>4,94%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>25317</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>16256</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>36614</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
           <t>2,0%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>5,52%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>20278</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>8692</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>31789</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>42802</t>
+          <t>49503</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>28250</t>
+          <t>37636</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>62078</t>
+          <t>67633</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>59730</t>
+          <t>72096</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>45206</t>
+          <t>54727</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>78604</t>
+          <t>94297</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>44323</t>
+          <t>56637</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20609</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63144</t>
+          <t>71606</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>104053</t>
+          <t>128733</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68836</t>
+          <t>106501</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>131444</t>
+          <t>155706</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>616835</t>
+          <t>701208</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>592919</t>
+          <t>675226</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>636305</t>
+          <t>722727</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>860868</t>
+          <t>723849</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>832415</t>
+          <t>704848</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>900440</t>
+          <t>740074</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1477702</t>
+          <t>1425058</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1438534</t>
+          <t>1393643</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1530410</t>
+          <t>1450570</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>89,8%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>9338</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3486</t>
+          <t>4514</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16230</t>
+          <t>16737</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4664</t>
+          <t>5379</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9418</t>
+          <t>10280</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>12963</t>
+          <t>14717</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7397</t>
+          <t>8599</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22306</t>
+          <t>23990</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>32600</t>
+          <t>40200</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22940</t>
+          <t>29326</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44830</t>
+          <t>55863</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>36100</t>
+          <t>42911</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25701</t>
+          <t>32592</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48389</t>
+          <t>56784</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>68700</t>
+          <t>83111</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>52617</t>
+          <t>66959</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>84792</t>
+          <t>101111</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>113109</t>
+          <t>133857</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>92945</t>
+          <t>111048</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>136327</t>
+          <t>157643</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>135691</t>
+          <t>153896</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>109279</t>
+          <t>134965</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>159713</t>
+          <t>176098</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>248801</t>
+          <t>287753</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>215408</t>
+          <t>258274</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>280567</t>
+          <t>320141</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>772823</t>
+          <t>806667</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>743859</t>
+          <t>775839</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>795281</t>
+          <t>831785</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>918477</t>
+          <t>916855</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>891568</t>
+          <t>891389</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>951544</t>
+          <t>938108</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1691300</t>
+          <t>1723523</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1656213</t>
+          <t>1687206</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1735298</t>
+          <t>1755811</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>83,25%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>22175</t>
+          <t>23530</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12120</t>
+          <t>14058</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>36691</t>
+          <t>36819</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>20614</t>
+          <t>21386</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12864</t>
+          <t>13767</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>39492</t>
+          <t>34259</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>42789</t>
+          <t>44916</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>30209</t>
+          <t>32264</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>66446</t>
+          <t>62666</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>103920</t>
+          <t>123153</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>78830</t>
+          <t>101307</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>129856</t>
+          <t>150312</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>109731</t>
+          <t>129808</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>85867</t>
+          <t>111519</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>132514</t>
+          <t>153597</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>213650</t>
+          <t>252961</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>178767</t>
+          <t>220220</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>248984</t>
+          <t>285372</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>284135</t>
+          <t>334505</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>227212</t>
+          <t>296308</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>328963</t>
+          <t>371703</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>316467</t>
+          <t>367642</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>258908</t>
+          <t>334313</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>353173</t>
+          <t>401881</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>600602</t>
+          <t>702147</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>516364</t>
+          <t>646586</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>661283</t>
+          <t>752580</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3049587</t>
+          <t>3051574</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2992170</t>
+          <t>3000343</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3137027</t>
+          <t>3096532</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3265469</t>
+          <t>3218118</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3217920</t>
+          <t>3176703</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3349284</t>
+          <t>3255797</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>6315056</t>
+          <t>6269692</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6237420</t>
+          <t>6207759</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6439604</t>
+          <t>6331232</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>87,09%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
